--- a/data/curva_de_sun.xlsx
+++ b/data/curva_de_sun.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:N23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,25 +457,45 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>05dec2025</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>06dec2025</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>07dec2025</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>08dec2025</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -500,18 +520,30 @@
         <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2" t="n">
+        <v>5</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
         <v>2</v>
       </c>
-      <c r="H2" t="n">
+      <c r="L2" t="n">
         <v>6</v>
       </c>
-      <c r="I2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J2" t="n">
+      <c r="M2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -534,18 +566,30 @@
         <v>4</v>
       </c>
       <c r="F3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G3" t="n">
         <v>3</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>3</v>
+      </c>
+      <c r="K3" t="n">
         <v>6</v>
       </c>
-      <c r="H3" t="n">
+      <c r="L3" t="n">
         <v>1</v>
       </c>
-      <c r="I3" t="n">
+      <c r="M3" t="n">
         <v>24</v>
       </c>
-      <c r="J3" t="n">
+      <c r="N3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -568,18 +612,30 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G4" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>10</v>
+      </c>
+      <c r="L4" t="n">
+        <v>10</v>
+      </c>
+      <c r="M4" t="n">
         <v>8</v>
       </c>
-      <c r="J4" t="n">
+      <c r="N4" t="n">
         <v>9</v>
       </c>
     </row>
@@ -602,18 +658,30 @@
         <v>2</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G5" t="n">
+        <v>5</v>
+      </c>
+      <c r="H5" t="n">
+        <v>4</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
         <v>6</v>
       </c>
-      <c r="H5" t="n">
+      <c r="L5" t="n">
         <v>9</v>
       </c>
-      <c r="I5" t="n">
-        <v>10</v>
-      </c>
-      <c r="J5" t="n">
+      <c r="M5" t="n">
+        <v>10</v>
+      </c>
+      <c r="N5" t="n">
         <v>8</v>
       </c>
     </row>
@@ -636,18 +704,30 @@
         <v>2</v>
       </c>
       <c r="F6" t="n">
+        <v>4</v>
+      </c>
+      <c r="G6" t="n">
+        <v>5</v>
+      </c>
+      <c r="H6" t="n">
+        <v>5</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
         <v>3</v>
       </c>
-      <c r="G6" t="n">
+      <c r="K6" t="n">
         <v>6</v>
       </c>
-      <c r="H6" t="n">
-        <v>10</v>
-      </c>
-      <c r="I6" t="n">
+      <c r="L6" t="n">
+        <v>10</v>
+      </c>
+      <c r="M6" t="n">
         <v>9</v>
       </c>
-      <c r="J6" t="n">
+      <c r="N6" t="n">
         <v>10</v>
       </c>
     </row>
@@ -670,18 +750,30 @@
         <v>3</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G7" t="n">
+        <v>5</v>
+      </c>
+      <c r="H7" t="n">
+        <v>4</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
         <v>6</v>
       </c>
-      <c r="H7" t="n">
+      <c r="L7" t="n">
         <v>12</v>
       </c>
-      <c r="I7" t="n">
-        <v>10</v>
-      </c>
-      <c r="J7" t="n">
+      <c r="M7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -704,18 +796,30 @@
         <v>1</v>
       </c>
       <c r="F8" t="n">
+        <v>5</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H8" t="n">
+        <v>5</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
         <v>1</v>
       </c>
-      <c r="G8" t="n">
+      <c r="K8" t="n">
         <v>9</v>
       </c>
-      <c r="H8" t="n">
-        <v>10</v>
-      </c>
-      <c r="I8" t="n">
+      <c r="L8" t="n">
+        <v>10</v>
+      </c>
+      <c r="M8" t="n">
         <v>9</v>
       </c>
-      <c r="J8" t="n">
+      <c r="N8" t="n">
         <v>9</v>
       </c>
     </row>
@@ -738,18 +842,30 @@
         <v>2</v>
       </c>
       <c r="F9" t="n">
+        <v>4</v>
+      </c>
+      <c r="G9" t="n">
+        <v>5</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
         <v>2</v>
       </c>
-      <c r="G9" t="n">
-        <v>5</v>
-      </c>
-      <c r="H9" t="n">
+      <c r="K9" t="n">
+        <v>5</v>
+      </c>
+      <c r="L9" t="n">
         <v>8</v>
       </c>
-      <c r="I9" t="n">
-        <v>10</v>
-      </c>
-      <c r="J9" t="n">
+      <c r="M9" t="n">
+        <v>10</v>
+      </c>
+      <c r="N9" t="n">
         <v>10</v>
       </c>
     </row>
@@ -772,18 +888,30 @@
         <v>3</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G10" t="n">
+        <v>5</v>
+      </c>
+      <c r="H10" t="n">
+        <v>5</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
         <v>12</v>
       </c>
-      <c r="H10" t="n">
+      <c r="L10" t="n">
         <v>11</v>
       </c>
-      <c r="I10" t="n">
-        <v>10</v>
-      </c>
-      <c r="J10" t="n">
+      <c r="M10" t="n">
+        <v>10</v>
+      </c>
+      <c r="N10" t="n">
         <v>12</v>
       </c>
     </row>
@@ -806,18 +934,30 @@
         <v>3</v>
       </c>
       <c r="F11" t="n">
+        <v>3</v>
+      </c>
+      <c r="G11" t="n">
+        <v>3</v>
+      </c>
+      <c r="H11" t="n">
         <v>1</v>
       </c>
-      <c r="G11" t="n">
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
         <v>9</v>
       </c>
-      <c r="H11" t="n">
+      <c r="L11" t="n">
         <v>8</v>
       </c>
-      <c r="I11" t="n">
+      <c r="M11" t="n">
         <v>9</v>
       </c>
-      <c r="J11" t="n">
+      <c r="N11" t="n">
         <v>10</v>
       </c>
     </row>
@@ -840,18 +980,30 @@
         <v>7</v>
       </c>
       <c r="F12" t="n">
+        <v>7</v>
+      </c>
+      <c r="G12" t="n">
+        <v>7</v>
+      </c>
+      <c r="H12" t="n">
+        <v>9</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
         <v>4</v>
       </c>
-      <c r="G12" t="n">
-        <v>10</v>
-      </c>
-      <c r="H12" t="n">
-        <v>10</v>
-      </c>
-      <c r="I12" t="n">
-        <v>10</v>
-      </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
+        <v>10</v>
+      </c>
+      <c r="L12" t="n">
+        <v>10</v>
+      </c>
+      <c r="M12" t="n">
+        <v>10</v>
+      </c>
+      <c r="N12" t="n">
         <v>10</v>
       </c>
     </row>
@@ -874,18 +1026,30 @@
         <v>3</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G13" t="n">
+        <v>5</v>
+      </c>
+      <c r="H13" t="n">
+        <v>5</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
         <v>11</v>
       </c>
-      <c r="H13" t="n">
-        <v>10</v>
-      </c>
-      <c r="I13" t="n">
+      <c r="L13" t="n">
+        <v>10</v>
+      </c>
+      <c r="M13" t="n">
         <v>8</v>
       </c>
-      <c r="J13" t="n">
+      <c r="N13" t="n">
         <v>12</v>
       </c>
     </row>
@@ -908,18 +1072,30 @@
         <v>4</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H14" t="n">
+        <v>6</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>5</v>
+      </c>
+      <c r="L14" t="n">
         <v>14</v>
       </c>
-      <c r="I14" t="n">
-        <v>10</v>
-      </c>
-      <c r="J14" t="n">
+      <c r="M14" t="n">
+        <v>10</v>
+      </c>
+      <c r="N14" t="n">
         <v>10</v>
       </c>
     </row>
@@ -942,18 +1118,30 @@
         <v>3</v>
       </c>
       <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>4</v>
+      </c>
+      <c r="H15" t="n">
+        <v>5</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
         <v>2</v>
       </c>
-      <c r="G15" t="n">
+      <c r="K15" t="n">
         <v>8</v>
       </c>
-      <c r="H15" t="n">
-        <v>10</v>
-      </c>
-      <c r="I15" t="n">
-        <v>10</v>
-      </c>
-      <c r="J15" t="n">
+      <c r="L15" t="n">
+        <v>10</v>
+      </c>
+      <c r="M15" t="n">
+        <v>10</v>
+      </c>
+      <c r="N15" t="n">
         <v>10</v>
       </c>
     </row>
@@ -976,18 +1164,30 @@
         <v>1</v>
       </c>
       <c r="F16" t="n">
+        <v>4</v>
+      </c>
+      <c r="G16" t="n">
         <v>2</v>
       </c>
-      <c r="G16" t="n">
+      <c r="H16" t="n">
+        <v>6</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2</v>
+      </c>
+      <c r="K16" t="n">
         <v>7</v>
       </c>
-      <c r="H16" t="n">
-        <v>10</v>
-      </c>
-      <c r="I16" t="n">
+      <c r="L16" t="n">
+        <v>10</v>
+      </c>
+      <c r="M16" t="n">
         <v>6</v>
       </c>
-      <c r="J16" t="n">
+      <c r="N16" t="n">
         <v>8</v>
       </c>
     </row>
@@ -1010,18 +1210,30 @@
         <v>2</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H17" t="n">
+        <v>4</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
         <v>9</v>
       </c>
-      <c r="H17" t="n">
-        <v>10</v>
-      </c>
-      <c r="I17" t="n">
+      <c r="L17" t="n">
+        <v>10</v>
+      </c>
+      <c r="M17" t="n">
         <v>4</v>
       </c>
-      <c r="J17" t="n">
+      <c r="N17" t="n">
         <v>8</v>
       </c>
     </row>
@@ -1044,18 +1256,30 @@
         <v>6</v>
       </c>
       <c r="F18" t="n">
+        <v>4</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>10</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
         <v>1</v>
       </c>
-      <c r="G18" t="n">
-        <v>10</v>
-      </c>
-      <c r="H18" t="n">
+      <c r="K18" t="n">
+        <v>10</v>
+      </c>
+      <c r="L18" t="n">
         <v>12</v>
       </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
         <v>11</v>
       </c>
     </row>
@@ -1078,18 +1302,30 @@
         <v>3</v>
       </c>
       <c r="F19" t="n">
+        <v>5</v>
+      </c>
+      <c r="G19" t="n">
+        <v>5</v>
+      </c>
+      <c r="H19" t="n">
+        <v>5</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
         <v>1</v>
       </c>
-      <c r="G19" t="n">
+      <c r="K19" t="n">
         <v>8</v>
       </c>
-      <c r="H19" t="n">
+      <c r="L19" t="n">
         <v>11</v>
       </c>
-      <c r="I19" t="n">
+      <c r="M19" t="n">
         <v>7</v>
       </c>
-      <c r="J19" t="n">
+      <c r="N19" t="n">
         <v>10</v>
       </c>
     </row>
@@ -1112,18 +1348,30 @@
         <v>3</v>
       </c>
       <c r="F20" t="n">
+        <v>5</v>
+      </c>
+      <c r="G20" t="n">
+        <v>5</v>
+      </c>
+      <c r="H20" t="n">
+        <v>5</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
         <v>2</v>
       </c>
-      <c r="G20" t="n">
+      <c r="K20" t="n">
         <v>9</v>
       </c>
-      <c r="H20" t="n">
-        <v>10</v>
-      </c>
-      <c r="I20" t="n">
-        <v>10</v>
-      </c>
-      <c r="J20" t="n">
+      <c r="L20" t="n">
+        <v>10</v>
+      </c>
+      <c r="M20" t="n">
+        <v>10</v>
+      </c>
+      <c r="N20" t="n">
         <v>10</v>
       </c>
     </row>
@@ -1158,6 +1406,18 @@
         <v>0</v>
       </c>
       <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1180,18 +1440,30 @@
         <v>3</v>
       </c>
       <c r="F22" t="n">
+        <v>3</v>
+      </c>
+      <c r="G22" t="n">
+        <v>5</v>
+      </c>
+      <c r="H22" t="n">
+        <v>5</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
         <v>1</v>
       </c>
-      <c r="G22" t="n">
+      <c r="K22" t="n">
         <v>11</v>
       </c>
-      <c r="H22" t="n">
-        <v>10</v>
-      </c>
-      <c r="I22" t="n">
+      <c r="L22" t="n">
+        <v>10</v>
+      </c>
+      <c r="M22" t="n">
         <v>9</v>
       </c>
-      <c r="J22" t="n">
+      <c r="N22" t="n">
         <v>11</v>
       </c>
     </row>
@@ -1214,18 +1486,30 @@
         <v>3</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G23" t="n">
+        <v>5</v>
+      </c>
+      <c r="H23" t="n">
+        <v>3</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
         <v>7</v>
       </c>
-      <c r="H23" t="n">
+      <c r="L23" t="n">
         <v>9</v>
       </c>
-      <c r="I23" t="n">
+      <c r="M23" t="n">
         <v>9</v>
       </c>
-      <c r="J23" t="n">
+      <c r="N23" t="n">
         <v>10</v>
       </c>
     </row>
@@ -1240,7 +1524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:N23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1271,25 +1555,45 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>05dec2025</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>06dec2025</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>07dec2025</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>08dec2025</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -1321,23 +1625,39 @@
           <t>1</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -1363,25 +1683,41 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -1401,23 +1737,39 @@
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -1449,23 +1801,43 @@
           <t>2</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -1499,25 +1871,41 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -1549,23 +1937,39 @@
           <t>3</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -1595,25 +1999,41 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -1647,25 +2067,41 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -1697,23 +2133,43 @@
           <t>3</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="G10" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -1747,25 +2203,41 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -1799,25 +2271,41 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -1849,23 +2337,43 @@
           <t>3</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="G13" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -1897,23 +2405,39 @@
           <t>4</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -1945,27 +2469,39 @@
           <t>3</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -1999,25 +2535,41 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -2045,23 +2597,39 @@
           <t>2</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="G17" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -2091,22 +2659,34 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
@@ -2139,25 +2719,41 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -2191,25 +2787,41 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -2229,7 +2841,11 @@
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr">
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -2263,25 +2879,41 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -2313,23 +2945,39 @@
           <t>3</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="G23" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t>10</t>
         </is>

--- a/data/curva_de_sun.xlsx
+++ b/data/curva_de_sun.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N23"/>
+  <dimension ref="A1:O24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -477,25 +477,30 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>09dec2025</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -504,66 +509,69 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>ALVITES CAMPOS SERGIO MARTIN</t>
+          <t>74212151</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>ANGIE BELÉN RODRÍGUEZ ZAVALA</t>
+          <t>ALVITES CAMPOS SERGIO MARTIN</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
         <v>4</v>
@@ -572,111 +580,117 @@
         <v>3</v>
       </c>
       <c r="H3" t="n">
+        <v>5</v>
+      </c>
+      <c r="I3" t="n">
         <v>2</v>
       </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
       <c r="J3" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>2</v>
+      </c>
+      <c r="M3" t="n">
         <v>6</v>
       </c>
-      <c r="L3" t="n">
-        <v>1</v>
-      </c>
-      <c r="M3" t="n">
-        <v>24</v>
-      </c>
       <c r="N3" t="n">
+        <v>5</v>
+      </c>
+      <c r="O3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>ARANEDA LOPEZ MARCO VIERI</t>
+          <t>ANGIE BELÉN RODRÍGUEZ ZAVALA</t>
         </is>
       </c>
       <c r="B4" t="n">
+        <v>18</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>8</v>
+      </c>
+      <c r="E4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F4" t="n">
+        <v>4</v>
+      </c>
+      <c r="G4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I4" t="n">
+        <v>9</v>
+      </c>
+      <c r="J4" t="n">
+        <v>6</v>
+      </c>
+      <c r="K4" t="n">
+        <v>3</v>
+      </c>
+      <c r="L4" t="n">
+        <v>6</v>
+      </c>
+      <c r="M4" t="n">
         <v>1</v>
       </c>
-      <c r="C4" t="n">
-        <v>12</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>5</v>
-      </c>
-      <c r="G4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H4" t="n">
-        <v>6</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>10</v>
-      </c>
-      <c r="L4" t="n">
-        <v>10</v>
-      </c>
-      <c r="M4" t="n">
-        <v>8</v>
-      </c>
       <c r="N4" t="n">
-        <v>9</v>
+        <v>24</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>BAZAN TEJADA JOSE VICENTE</t>
+          <t>ARANEDA LOPEZ MARCO VIERI</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>5</v>
+      </c>
+      <c r="G5" t="n">
         <v>2</v>
       </c>
-      <c r="F5" t="n">
-        <v>4</v>
-      </c>
-      <c r="G5" t="n">
-        <v>5</v>
-      </c>
       <c r="H5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M5" t="n">
         <v>10</v>
@@ -684,11 +698,14 @@
       <c r="N5" t="n">
         <v>8</v>
       </c>
+      <c r="O5" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>CARBAJAL RAMOS JESUS MARINA</t>
+          <t>BAZAN TEJADA JOSE VICENTE</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -698,7 +715,7 @@
         <v>7</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
         <v>2</v>
@@ -710,19 +727,19 @@
         <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J6" t="n">
         <v>3</v>
       </c>
       <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
         <v>6</v>
-      </c>
-      <c r="L6" t="n">
-        <v>10</v>
       </c>
       <c r="M6" t="n">
         <v>9</v>
@@ -730,24 +747,27 @@
       <c r="N6" t="n">
         <v>10</v>
       </c>
+      <c r="O6" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>CARDENAS CAMPOJO MARY PAULA</t>
+          <t>CARBAJAL RAMOS JESUS MARINA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D7" t="n">
         <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F7" t="n">
         <v>4</v>
@@ -756,495 +776,528 @@
         <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L7" t="n">
         <v>6</v>
       </c>
-      <c r="L7" t="n">
-        <v>12</v>
-      </c>
       <c r="M7" t="n">
         <v>10</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>9</v>
+      </c>
+      <c r="O7" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>CASTILLO QUEZADA DIEGO ALONSO</t>
+          <t>CARDENAS CAMPOJO MARY PAULA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C8" t="n">
+        <v>5</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" t="n">
         <v>3</v>
       </c>
-      <c r="D8" t="n">
-        <v>3</v>
-      </c>
-      <c r="E8" t="n">
-        <v>1</v>
-      </c>
       <c r="F8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K8" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M8" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="N8" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>DANY DARWIN VILLACORTA SAAVEDRA</t>
+          <t>CASTILLO QUEZADA DIEGO ALONSO</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
         <v>4</v>
       </c>
       <c r="G9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
+        <v>5</v>
+      </c>
+      <c r="I9" t="n">
+        <v>4</v>
+      </c>
+      <c r="J9" t="n">
         <v>3</v>
       </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2</v>
-      </c>
       <c r="K9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M9" t="n">
         <v>10</v>
       </c>
       <c r="N9" t="n">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="O9" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>DAVILA CORDOVA MARIBEL</t>
+          <t>DANY DARWIN VILLACORTA SAAVEDRA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C10" t="n">
         <v>7</v>
       </c>
       <c r="D10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" t="n">
         <v>4</v>
       </c>
-      <c r="E10" t="n">
+      <c r="G10" t="n">
+        <v>5</v>
+      </c>
+      <c r="H10" t="n">
         <v>3</v>
       </c>
-      <c r="F10" t="n">
-        <v>5</v>
-      </c>
-      <c r="G10" t="n">
-        <v>5</v>
-      </c>
-      <c r="H10" t="n">
-        <v>5</v>
-      </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K10" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="L10" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="M10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="N10" t="n">
-        <v>12</v>
+        <v>10</v>
+      </c>
+      <c r="O10" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>DELGADO DELGADO RONI</t>
+          <t>DAVILA CORDOVA MARIBEL</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E11" t="n">
         <v>3</v>
       </c>
       <c r="F11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K11" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="M11" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="N11" t="n">
         <v>10</v>
+      </c>
+      <c r="O11" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>FARFAN MONTOYA ROSSANA ISABEL</t>
+          <t>DELGADO DELGADO RONI</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>9</v>
       </c>
       <c r="C12" t="n">
+        <v>5</v>
+      </c>
+      <c r="D12" t="n">
+        <v>3</v>
+      </c>
+      <c r="E12" t="n">
+        <v>3</v>
+      </c>
+      <c r="F12" t="n">
+        <v>3</v>
+      </c>
+      <c r="G12" t="n">
+        <v>3</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" t="n">
         <v>9</v>
       </c>
-      <c r="D12" t="n">
+      <c r="M12" t="n">
+        <v>8</v>
+      </c>
+      <c r="N12" t="n">
         <v>9</v>
       </c>
-      <c r="E12" t="n">
-        <v>7</v>
-      </c>
-      <c r="F12" t="n">
-        <v>7</v>
-      </c>
-      <c r="G12" t="n">
-        <v>7</v>
-      </c>
-      <c r="H12" t="n">
-        <v>9</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>4</v>
-      </c>
-      <c r="K12" t="n">
-        <v>10</v>
-      </c>
-      <c r="L12" t="n">
-        <v>10</v>
-      </c>
-      <c r="M12" t="n">
-        <v>10</v>
-      </c>
-      <c r="N12" t="n">
+      <c r="O12" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>FIORELA KEILY GUTIERREZ CRUZ</t>
+          <t>FARFAN MONTOYA ROSSANA ISABEL</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E13" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F13" t="n">
+        <v>7</v>
+      </c>
+      <c r="G13" t="n">
+        <v>7</v>
+      </c>
+      <c r="H13" t="n">
+        <v>9</v>
+      </c>
+      <c r="I13" t="n">
+        <v>10</v>
+      </c>
+      <c r="J13" t="n">
+        <v>10</v>
+      </c>
+      <c r="K13" t="n">
         <v>4</v>
       </c>
-      <c r="G13" t="n">
-        <v>5</v>
-      </c>
-      <c r="H13" t="n">
-        <v>5</v>
-      </c>
-      <c r="I13" t="n">
-        <v>1</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>11</v>
-      </c>
       <c r="L13" t="n">
         <v>10</v>
       </c>
       <c r="M13" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N13" t="n">
-        <v>12</v>
+        <v>10</v>
+      </c>
+      <c r="O13" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>GARCIA GUTIERREZ LUIS ARTURO</t>
+          <t>FIORELA KEILY GUTIERREZ CRUZ</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
         <v>6</v>
       </c>
       <c r="D14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" t="n">
         <v>3</v>
-      </c>
-      <c r="E14" t="n">
-        <v>4</v>
       </c>
       <c r="F14" t="n">
         <v>4</v>
       </c>
       <c r="G14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H14" t="n">
+        <v>5</v>
+      </c>
+      <c r="I14" t="n">
         <v>6</v>
       </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K14" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="M14" t="n">
         <v>10</v>
       </c>
       <c r="N14" t="n">
-        <v>10</v>
+        <v>8</v>
+      </c>
+      <c r="O14" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>GONZALES VALLE SEBASTIAN</t>
+          <t>GARCIA GUTIERREZ LUIS ARTURO</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D15" t="n">
         <v>3</v>
       </c>
       <c r="E15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G15" t="n">
         <v>4</v>
       </c>
       <c r="H15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J15" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="K15" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="M15" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="N15" t="n">
+        <v>10</v>
+      </c>
+      <c r="O15" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>GUERRA CALDERON ESTHEFANY NICOLLE</t>
+          <t>GONZALES VALLE SEBASTIAN</t>
         </is>
       </c>
       <c r="B16" t="n">
+        <v>5</v>
+      </c>
+      <c r="C16" t="n">
+        <v>7</v>
+      </c>
+      <c r="D16" t="n">
+        <v>3</v>
+      </c>
+      <c r="E16" t="n">
+        <v>3</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>4</v>
+      </c>
+      <c r="H16" t="n">
+        <v>5</v>
+      </c>
+      <c r="I16" t="n">
+        <v>4</v>
+      </c>
+      <c r="J16" t="n">
+        <v>4</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2</v>
+      </c>
+      <c r="L16" t="n">
         <v>8</v>
       </c>
-      <c r="C16" t="n">
-        <v>4</v>
-      </c>
-      <c r="D16" t="n">
-        <v>2</v>
-      </c>
-      <c r="E16" t="n">
-        <v>1</v>
-      </c>
-      <c r="F16" t="n">
-        <v>4</v>
-      </c>
-      <c r="G16" t="n">
-        <v>2</v>
-      </c>
-      <c r="H16" t="n">
-        <v>6</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>2</v>
-      </c>
-      <c r="K16" t="n">
-        <v>7</v>
-      </c>
-      <c r="L16" t="n">
-        <v>10</v>
-      </c>
       <c r="M16" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="N16" t="n">
-        <v>8</v>
+        <v>10</v>
+      </c>
+      <c r="O16" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>JAVE CHAVEZ ANGHELO MARTIN</t>
+          <t>GUERRA CALDERON ESTHEFANY NICOLLE</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D17" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F17" t="n">
         <v>4</v>
       </c>
       <c r="G17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H17" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K17" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="L17" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="M17" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="N17" t="n">
+        <v>6</v>
+      </c>
+      <c r="O17" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>JOSSY IVANA SUÁREZ ZAVALETA</t>
+          <t>JAVE CHAVEZ ANGHELO MARTIN</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
@@ -1253,96 +1306,102 @@
         <v>5</v>
       </c>
       <c r="E18" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F18" t="n">
         <v>4</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H18" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K18" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N18" t="n">
-        <v>11</v>
+        <v>4</v>
+      </c>
+      <c r="O18" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>OLIVA ALVA GOSSELYN NASSIRA</t>
+          <t>JOSSY IVANA SUÁREZ ZAVALETA</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>10</v>
       </c>
       <c r="C19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" t="n">
+        <v>5</v>
+      </c>
+      <c r="E19" t="n">
+        <v>6</v>
+      </c>
+      <c r="F19" t="n">
         <v>4</v>
       </c>
-      <c r="D19" t="n">
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>10</v>
+      </c>
+      <c r="I19" t="n">
+        <v>3</v>
+      </c>
+      <c r="J19" t="n">
+        <v>4</v>
+      </c>
+      <c r="K19" t="n">
         <v>1</v>
       </c>
-      <c r="E19" t="n">
-        <v>3</v>
-      </c>
-      <c r="F19" t="n">
-        <v>5</v>
-      </c>
-      <c r="G19" t="n">
-        <v>5</v>
-      </c>
-      <c r="H19" t="n">
-        <v>5</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1</v>
-      </c>
-      <c r="K19" t="n">
-        <v>8</v>
-      </c>
       <c r="L19" t="n">
+        <v>10</v>
+      </c>
+      <c r="M19" t="n">
+        <v>12</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
         <v>11</v>
-      </c>
-      <c r="M19" t="n">
-        <v>7</v>
-      </c>
-      <c r="N19" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>RAMOS RAMOS HANDY JAIR</t>
+          <t>OLIVA ALVA GOSSELYN NASSIRA</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E20" t="n">
         <v>3</v>
@@ -1357,159 +1416,220 @@
         <v>5</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J20" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K20" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="L20" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="M20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N20" t="n">
+        <v>7</v>
+      </c>
+      <c r="O20" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>ROCHA SIPIRAN JHORDAN ENRIQUE</t>
+          <t>RAMOS RAMOS HANDY JAIR</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N21" t="n">
-        <v>1</v>
+        <v>10</v>
+      </c>
+      <c r="O21" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>SANCHEZ ULLOA CESAR AUGUSTO</t>
+          <t>ROCHA SIPIRAN JHORDAN ENRIQUE</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
       <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
         <v>1</v>
-      </c>
-      <c r="K22" t="n">
-        <v>11</v>
-      </c>
-      <c r="L22" t="n">
-        <v>10</v>
-      </c>
-      <c r="M22" t="n">
-        <v>9</v>
-      </c>
-      <c r="N22" t="n">
-        <v>11</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>VERDE LIZARRAGA DEYSI EUFEMIA</t>
+          <t>SANCHEZ ULLOA CESAR AUGUSTO</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C23" t="n">
+        <v>6</v>
+      </c>
+      <c r="D23" t="n">
         <v>3</v>
-      </c>
-      <c r="D23" t="n">
-        <v>5</v>
       </c>
       <c r="E23" t="n">
         <v>3</v>
       </c>
       <c r="F23" t="n">
+        <v>3</v>
+      </c>
+      <c r="G23" t="n">
+        <v>5</v>
+      </c>
+      <c r="H23" t="n">
+        <v>5</v>
+      </c>
+      <c r="I23" t="n">
+        <v>6</v>
+      </c>
+      <c r="J23" t="n">
+        <v>6</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1</v>
+      </c>
+      <c r="L23" t="n">
+        <v>11</v>
+      </c>
+      <c r="M23" t="n">
+        <v>10</v>
+      </c>
+      <c r="N23" t="n">
+        <v>9</v>
+      </c>
+      <c r="O23" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>VERDE LIZARRAGA DEYSI EUFEMIA</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>10</v>
+      </c>
+      <c r="C24" t="n">
+        <v>3</v>
+      </c>
+      <c r="D24" t="n">
+        <v>5</v>
+      </c>
+      <c r="E24" t="n">
+        <v>3</v>
+      </c>
+      <c r="F24" t="n">
         <v>4</v>
       </c>
-      <c r="G23" t="n">
-        <v>5</v>
-      </c>
-      <c r="H23" t="n">
+      <c r="G24" t="n">
+        <v>5</v>
+      </c>
+      <c r="H24" t="n">
         <v>3</v>
       </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
+      <c r="I24" t="n">
+        <v>8</v>
+      </c>
+      <c r="J24" t="n">
+        <v>8</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
         <v>7</v>
       </c>
-      <c r="L23" t="n">
+      <c r="M24" t="n">
         <v>9</v>
       </c>
-      <c r="M23" t="n">
+      <c r="N24" t="n">
         <v>9</v>
       </c>
-      <c r="N23" t="n">
+      <c r="O24" t="n">
         <v>10</v>
       </c>
     </row>
@@ -1524,7 +1644,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N23"/>
+  <dimension ref="A1:O24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1575,25 +1695,30 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>09dec2025</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -1602,90 +1727,59 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>ALVITES CAMPOS SERGIO MARTIN</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>74212151</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>ANGIE BELÉN RODRÍGUEZ ZAVALA</t>
+          <t>ALVITES CAMPOS SERGIO MARTIN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>3</t>
@@ -1693,160 +1787,171 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>ARANEDA LOPEZ MARCO VIERI</t>
+          <t>ANGIE BELÉN RODRÍGUEZ ZAVALA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>BAZAN TEJADA JOSE VICENTE</t>
+          <t>ARANEDA LOPEZ MARCO VIERI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>CARBAJAL RAMOS JESUS MARINA</t>
+          <t>BAZAN TEJADA JOSE VICENTE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1861,14 +1966,14 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>4</t>
@@ -1881,25 +1986,25 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="M6" t="inlineStr">
         <is>
           <t>9</t>
@@ -1908,23 +2013,28 @@
       <c r="N6" t="inlineStr">
         <is>
           <t>10</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>CARDENAS CAMPOJO MARY PAULA</t>
+          <t>CARBAJAL RAMOS JESUS MARINA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1934,166 +2044,188 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="M7" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>CASTILLO QUEZADA DIEGO ALONSO</t>
+          <t>CARDENAS CAMPOJO MARY PAULA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>12</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>DANY DARWIN VILLACORTA SAAVEDRA</t>
+          <t>CASTILLO QUEZADA DIEGO ALONSO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -2103,19 +2235,24 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>9</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>DAVILA CORDOVA MARIBEL</t>
+          <t>DANY DARWIN VILLACORTA SAAVEDRA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2125,128 +2262,138 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>DELGADO DELGADO RONI</t>
+          <t>DAVILA CORDOVA MARIBEL</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
           <t>10</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>12</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>FARFAN MONTOYA ROSSANA ISABEL</t>
+          <t>DELGADO DELGADO RONI</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2256,56 +2403,61 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -2314,55 +2466,59 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>FIORELA KEILY GUTIERREZ CRUZ</t>
+          <t>FARFAN MONTOYA ROSSANA ISABEL</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>10</t>
@@ -2370,24 +2526,29 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>GARCIA GUTIERREZ LUIS ARTURO</t>
+          <t>FIORELA KEILY GUTIERREZ CRUZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2397,39 +2558,43 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -2439,69 +2604,83 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>12</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>GONZALES VALLE SEBASTIAN</t>
+          <t>GARCIA GUTIERREZ LUIS ARTURO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
           <t>8</t>
         </is>
       </c>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>14</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -2510,126 +2689,144 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>GUERRA CALDERON ESTHEFANY NICOLLE</t>
+          <t>GONZALES VALLE SEBASTIAN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>JAVE CHAVEZ ANGHELO MARTIN</t>
+          <t>GUERRA CALDERON ESTHEFANY NICOLLE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -2638,12 +2835,12 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>JOSSY IVANA SUÁREZ ZAVALETA</t>
+          <t>JAVE CHAVEZ ANGHELO MARTIN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
@@ -2654,7 +2851,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2662,39 +2859,52 @@
           <t>4</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr"/>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>OLIVA ALVA GOSSELYN NASSIRA</t>
+          <t>JOSSY IVANA SUÁREZ ZAVALETA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2702,82 +2912,79 @@
           <t>10</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="L19" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr">
+        <is>
           <t>11</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>10</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>RAMOS RAMOS HANDY JAIR</t>
+          <t>OLIVA ALVA GOSSELYN NASSIRA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2800,28 +3007,37 @@
           <t>5</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -2830,154 +3046,250 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>ROCHA SIPIRAN JHORDAN ENRIQUE</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
+          <t>RAMOS RAMOS HANDY JAIR</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>SANCHEZ ULLOA CESAR AUGUSTO</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>ROCHA SIPIRAN JHORDAN ENRIQUE</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr">
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>11</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
+          <t>SANCHEZ ULLOA CESAR AUGUSTO</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
           <t>VERDE LIZARRAGA DEYSI EUFEMIA</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="O24" t="inlineStr">
         <is>
           <t>10</t>
         </is>

--- a/data/curva_de_sun.xlsx
+++ b/data/curva_de_sun.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O24"/>
+  <dimension ref="A1:P24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,25 +482,30 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>10dec2025</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -554,6 +559,9 @@
       <c r="O2" t="n">
         <v>0</v>
       </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -592,15 +600,18 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
         <v>2</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>6</v>
       </c>
-      <c r="N3" t="n">
-        <v>5</v>
-      </c>
       <c r="O3" t="n">
+        <v>5</v>
+      </c>
+      <c r="P3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -638,18 +649,21 @@
         <v>6</v>
       </c>
       <c r="K4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>3</v>
+      </c>
+      <c r="M4" t="n">
         <v>6</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>1</v>
       </c>
-      <c r="N4" t="n">
+      <c r="O4" t="n">
         <v>24</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -687,18 +701,21 @@
         <v>5</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L5" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
         <v>10</v>
       </c>
       <c r="N5" t="n">
+        <v>10</v>
+      </c>
+      <c r="O5" t="n">
         <v>8</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>9</v>
       </c>
     </row>
@@ -736,18 +753,21 @@
         <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
         <v>6</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>9</v>
       </c>
-      <c r="N6" t="n">
-        <v>10</v>
-      </c>
       <c r="O6" t="n">
+        <v>10</v>
+      </c>
+      <c r="P6" t="n">
         <v>8</v>
       </c>
     </row>
@@ -785,18 +805,21 @@
         <v>7</v>
       </c>
       <c r="K7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M7" t="n">
         <v>6</v>
       </c>
-      <c r="M7" t="n">
-        <v>10</v>
-      </c>
       <c r="N7" t="n">
+        <v>10</v>
+      </c>
+      <c r="O7" t="n">
         <v>9</v>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>10</v>
       </c>
     </row>
@@ -834,18 +857,21 @@
         <v>6</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
         <v>6</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>12</v>
       </c>
-      <c r="N8" t="n">
-        <v>10</v>
-      </c>
       <c r="O8" t="n">
+        <v>10</v>
+      </c>
+      <c r="P8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -883,20 +909,23 @@
         <v>3</v>
       </c>
       <c r="K9" t="n">
+        <v>6</v>
+      </c>
+      <c r="L9" t="n">
         <v>1</v>
       </c>
-      <c r="L9" t="n">
+      <c r="M9" t="n">
         <v>9</v>
       </c>
-      <c r="M9" t="n">
-        <v>10</v>
-      </c>
       <c r="N9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O9" t="n">
         <v>9</v>
       </c>
+      <c r="P9" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -932,18 +961,21 @@
         <v>5</v>
       </c>
       <c r="K10" t="n">
+        <v>12</v>
+      </c>
+      <c r="L10" t="n">
         <v>2</v>
       </c>
-      <c r="L10" t="n">
-        <v>5</v>
-      </c>
       <c r="M10" t="n">
+        <v>5</v>
+      </c>
+      <c r="N10" t="n">
         <v>8</v>
       </c>
-      <c r="N10" t="n">
-        <v>10</v>
-      </c>
       <c r="O10" t="n">
+        <v>10</v>
+      </c>
+      <c r="P10" t="n">
         <v>10</v>
       </c>
     </row>
@@ -981,18 +1013,21 @@
         <v>6</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
         <v>12</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>11</v>
       </c>
-      <c r="N11" t="n">
-        <v>10</v>
-      </c>
       <c r="O11" t="n">
+        <v>10</v>
+      </c>
+      <c r="P11" t="n">
         <v>12</v>
       </c>
     </row>
@@ -1030,18 +1065,21 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
         <v>1</v>
       </c>
-      <c r="L12" t="n">
+      <c r="M12" t="n">
         <v>9</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>8</v>
       </c>
-      <c r="N12" t="n">
+      <c r="O12" t="n">
         <v>9</v>
       </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
         <v>10</v>
       </c>
     </row>
@@ -1079,11 +1117,11 @@
         <v>10</v>
       </c>
       <c r="K13" t="n">
+        <v>10</v>
+      </c>
+      <c r="L13" t="n">
         <v>4</v>
       </c>
-      <c r="L13" t="n">
-        <v>10</v>
-      </c>
       <c r="M13" t="n">
         <v>10</v>
       </c>
@@ -1091,6 +1129,9 @@
         <v>10</v>
       </c>
       <c r="O13" t="n">
+        <v>10</v>
+      </c>
+      <c r="P13" t="n">
         <v>10</v>
       </c>
     </row>
@@ -1128,18 +1169,21 @@
         <v>7</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
         <v>11</v>
       </c>
-      <c r="M14" t="n">
-        <v>10</v>
-      </c>
       <c r="N14" t="n">
+        <v>10</v>
+      </c>
+      <c r="O14" t="n">
         <v>8</v>
       </c>
-      <c r="O14" t="n">
+      <c r="P14" t="n">
         <v>12</v>
       </c>
     </row>
@@ -1177,18 +1221,21 @@
         <v>8</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L15" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
+        <v>5</v>
+      </c>
+      <c r="N15" t="n">
         <v>14</v>
       </c>
-      <c r="N15" t="n">
-        <v>10</v>
-      </c>
       <c r="O15" t="n">
+        <v>10</v>
+      </c>
+      <c r="P15" t="n">
         <v>10</v>
       </c>
     </row>
@@ -1226,18 +1273,21 @@
         <v>4</v>
       </c>
       <c r="K16" t="n">
+        <v>4</v>
+      </c>
+      <c r="L16" t="n">
         <v>2</v>
       </c>
-      <c r="L16" t="n">
+      <c r="M16" t="n">
         <v>8</v>
       </c>
-      <c r="M16" t="n">
-        <v>10</v>
-      </c>
       <c r="N16" t="n">
         <v>10</v>
       </c>
       <c r="O16" t="n">
+        <v>10</v>
+      </c>
+      <c r="P16" t="n">
         <v>10</v>
       </c>
     </row>
@@ -1275,18 +1325,21 @@
         <v>5</v>
       </c>
       <c r="K17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L17" t="n">
         <v>2</v>
       </c>
-      <c r="L17" t="n">
+      <c r="M17" t="n">
         <v>7</v>
       </c>
-      <c r="M17" t="n">
-        <v>10</v>
-      </c>
       <c r="N17" t="n">
+        <v>10</v>
+      </c>
+      <c r="O17" t="n">
         <v>6</v>
       </c>
-      <c r="O17" t="n">
+      <c r="P17" t="n">
         <v>8</v>
       </c>
     </row>
@@ -1324,18 +1377,21 @@
         <v>3</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
         <v>9</v>
       </c>
-      <c r="M18" t="n">
-        <v>10</v>
-      </c>
       <c r="N18" t="n">
+        <v>10</v>
+      </c>
+      <c r="O18" t="n">
         <v>4</v>
       </c>
-      <c r="O18" t="n">
+      <c r="P18" t="n">
         <v>8</v>
       </c>
     </row>
@@ -1373,18 +1429,21 @@
         <v>4</v>
       </c>
       <c r="K19" t="n">
+        <v>6</v>
+      </c>
+      <c r="L19" t="n">
         <v>1</v>
       </c>
-      <c r="L19" t="n">
-        <v>10</v>
-      </c>
       <c r="M19" t="n">
+        <v>10</v>
+      </c>
+      <c r="N19" t="n">
         <v>12</v>
       </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
       <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
         <v>11</v>
       </c>
     </row>
@@ -1422,18 +1481,21 @@
         <v>5</v>
       </c>
       <c r="K20" t="n">
+        <v>4</v>
+      </c>
+      <c r="L20" t="n">
         <v>1</v>
       </c>
-      <c r="L20" t="n">
+      <c r="M20" t="n">
         <v>8</v>
       </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
         <v>11</v>
       </c>
-      <c r="N20" t="n">
+      <c r="O20" t="n">
         <v>7</v>
       </c>
-      <c r="O20" t="n">
+      <c r="P20" t="n">
         <v>10</v>
       </c>
     </row>
@@ -1471,18 +1533,21 @@
         <v>6</v>
       </c>
       <c r="K21" t="n">
+        <v>5</v>
+      </c>
+      <c r="L21" t="n">
         <v>2</v>
       </c>
-      <c r="L21" t="n">
+      <c r="M21" t="n">
         <v>9</v>
       </c>
-      <c r="M21" t="n">
-        <v>10</v>
-      </c>
       <c r="N21" t="n">
         <v>10</v>
       </c>
       <c r="O21" t="n">
+        <v>10</v>
+      </c>
+      <c r="P21" t="n">
         <v>10</v>
       </c>
     </row>
@@ -1532,6 +1597,9 @@
         <v>0</v>
       </c>
       <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1569,18 +1637,21 @@
         <v>6</v>
       </c>
       <c r="K23" t="n">
+        <v>3</v>
+      </c>
+      <c r="L23" t="n">
         <v>1</v>
       </c>
-      <c r="L23" t="n">
+      <c r="M23" t="n">
         <v>11</v>
       </c>
-      <c r="M23" t="n">
-        <v>10</v>
-      </c>
       <c r="N23" t="n">
+        <v>10</v>
+      </c>
+      <c r="O23" t="n">
         <v>9</v>
       </c>
-      <c r="O23" t="n">
+      <c r="P23" t="n">
         <v>11</v>
       </c>
     </row>
@@ -1618,18 +1689,21 @@
         <v>8</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
         <v>7</v>
-      </c>
-      <c r="M24" t="n">
-        <v>9</v>
       </c>
       <c r="N24" t="n">
         <v>9</v>
       </c>
       <c r="O24" t="n">
+        <v>9</v>
+      </c>
+      <c r="P24" t="n">
         <v>10</v>
       </c>
     </row>
@@ -1644,7 +1718,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O24"/>
+  <dimension ref="A1:P24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1700,25 +1774,30 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>10dec2025</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -1748,6 +1827,7 @@
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -1801,22 +1881,23 @@
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr"/>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -1865,27 +1946,28 @@
           <t>6</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -1926,12 +2008,12 @@
           <t>5</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
           <t>10</t>
@@ -1939,10 +2021,15 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -1999,23 +2086,28 @@
           <t>3</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="O6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -2074,25 +2166,30 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -2149,23 +2246,28 @@
           <t>6</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr"/>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -2220,25 +2322,30 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -2293,25 +2400,30 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="M10" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="O10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -2368,23 +2480,28 @@
           <t>6</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr">
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="O11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -2437,27 +2554,28 @@
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -2516,14 +2634,14 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="M13" t="inlineStr">
         <is>
           <t>10</t>
@@ -2535,6 +2653,11 @@
         </is>
       </c>
       <c r="O13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -2591,23 +2714,28 @@
           <t>7</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr">
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -2664,23 +2792,28 @@
           <t>8</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="O15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -2735,25 +2868,30 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -2808,25 +2946,30 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="P17" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -2879,23 +3022,28 @@
           <t>3</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr">
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -2946,21 +3094,26 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="M19" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr">
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -3019,25 +3172,30 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -3096,25 +3254,30 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -3139,7 +3302,8 @@
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr">
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -3198,25 +3362,30 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
+      <c r="P23" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -3273,23 +3442,28 @@
           <t>8</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr">
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="O24" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
+      <c r="P24" t="inlineStr">
         <is>
           <t>10</t>
         </is>

--- a/data/curva_de_sun.xlsx
+++ b/data/curva_de_sun.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P24"/>
+  <dimension ref="A1:Q24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,25 +487,30 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>11dec2025</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -562,6 +567,9 @@
       <c r="P2" t="n">
         <v>0</v>
       </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -603,15 +611,18 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
         <v>2</v>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>6</v>
       </c>
-      <c r="O3" t="n">
-        <v>5</v>
-      </c>
       <c r="P3" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -652,18 +663,21 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="M4" t="n">
+        <v>3</v>
+      </c>
+      <c r="N4" t="n">
         <v>6</v>
       </c>
-      <c r="N4" t="n">
+      <c r="O4" t="n">
         <v>1</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>24</v>
       </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -704,18 +718,21 @@
         <v>9</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M5" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
         <v>10</v>
       </c>
       <c r="O5" t="n">
+        <v>10</v>
+      </c>
+      <c r="P5" t="n">
         <v>8</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
         <v>9</v>
       </c>
     </row>
@@ -756,18 +773,21 @@
         <v>4</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
         <v>6</v>
       </c>
-      <c r="N6" t="n">
+      <c r="O6" t="n">
         <v>9</v>
       </c>
-      <c r="O6" t="n">
-        <v>10</v>
-      </c>
       <c r="P6" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q6" t="n">
         <v>8</v>
       </c>
     </row>
@@ -808,18 +828,21 @@
         <v>5</v>
       </c>
       <c r="L7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M7" t="n">
+        <v>3</v>
+      </c>
+      <c r="N7" t="n">
         <v>6</v>
       </c>
-      <c r="N7" t="n">
-        <v>10</v>
-      </c>
       <c r="O7" t="n">
+        <v>10</v>
+      </c>
+      <c r="P7" t="n">
         <v>9</v>
       </c>
-      <c r="P7" t="n">
+      <c r="Q7" t="n">
         <v>10</v>
       </c>
     </row>
@@ -860,18 +883,21 @@
         <v>3</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
         <v>6</v>
       </c>
-      <c r="N8" t="n">
+      <c r="O8" t="n">
         <v>12</v>
       </c>
-      <c r="O8" t="n">
-        <v>10</v>
-      </c>
       <c r="P8" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -912,20 +938,23 @@
         <v>6</v>
       </c>
       <c r="L9" t="n">
+        <v>6</v>
+      </c>
+      <c r="M9" t="n">
         <v>1</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>9</v>
       </c>
-      <c r="N9" t="n">
-        <v>10</v>
-      </c>
       <c r="O9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P9" t="n">
         <v>9</v>
       </c>
+      <c r="Q9" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -964,18 +993,21 @@
         <v>12</v>
       </c>
       <c r="L10" t="n">
+        <v>3</v>
+      </c>
+      <c r="M10" t="n">
         <v>2</v>
       </c>
-      <c r="M10" t="n">
-        <v>5</v>
-      </c>
       <c r="N10" t="n">
+        <v>5</v>
+      </c>
+      <c r="O10" t="n">
         <v>8</v>
       </c>
-      <c r="O10" t="n">
-        <v>10</v>
-      </c>
       <c r="P10" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q10" t="n">
         <v>10</v>
       </c>
     </row>
@@ -1016,18 +1048,21 @@
         <v>4</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
         <v>12</v>
       </c>
-      <c r="N11" t="n">
+      <c r="O11" t="n">
         <v>11</v>
       </c>
-      <c r="O11" t="n">
-        <v>10</v>
-      </c>
       <c r="P11" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q11" t="n">
         <v>12</v>
       </c>
     </row>
@@ -1068,18 +1103,21 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
+        <v>2</v>
+      </c>
+      <c r="M12" t="n">
         <v>1</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>9</v>
       </c>
-      <c r="N12" t="n">
+      <c r="O12" t="n">
         <v>8</v>
       </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
         <v>9</v>
       </c>
-      <c r="P12" t="n">
+      <c r="Q12" t="n">
         <v>10</v>
       </c>
     </row>
@@ -1120,11 +1158,11 @@
         <v>10</v>
       </c>
       <c r="L13" t="n">
+        <v>12</v>
+      </c>
+      <c r="M13" t="n">
         <v>4</v>
       </c>
-      <c r="M13" t="n">
-        <v>10</v>
-      </c>
       <c r="N13" t="n">
         <v>10</v>
       </c>
@@ -1132,6 +1170,9 @@
         <v>10</v>
       </c>
       <c r="P13" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q13" t="n">
         <v>10</v>
       </c>
     </row>
@@ -1172,18 +1213,21 @@
         <v>5</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
         <v>11</v>
       </c>
-      <c r="N14" t="n">
-        <v>10</v>
-      </c>
       <c r="O14" t="n">
+        <v>10</v>
+      </c>
+      <c r="P14" t="n">
         <v>8</v>
       </c>
-      <c r="P14" t="n">
+      <c r="Q14" t="n">
         <v>12</v>
       </c>
     </row>
@@ -1224,18 +1268,21 @@
         <v>8</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M15" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
+        <v>5</v>
+      </c>
+      <c r="O15" t="n">
         <v>14</v>
       </c>
-      <c r="O15" t="n">
-        <v>10</v>
-      </c>
       <c r="P15" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q15" t="n">
         <v>10</v>
       </c>
     </row>
@@ -1276,18 +1323,21 @@
         <v>4</v>
       </c>
       <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
         <v>2</v>
       </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
         <v>8</v>
       </c>
-      <c r="N16" t="n">
-        <v>10</v>
-      </c>
       <c r="O16" t="n">
         <v>10</v>
       </c>
       <c r="P16" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q16" t="n">
         <v>10</v>
       </c>
     </row>
@@ -1328,18 +1378,21 @@
         <v>3</v>
       </c>
       <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
         <v>2</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>7</v>
       </c>
-      <c r="N17" t="n">
-        <v>10</v>
-      </c>
       <c r="O17" t="n">
+        <v>10</v>
+      </c>
+      <c r="P17" t="n">
         <v>6</v>
       </c>
-      <c r="P17" t="n">
+      <c r="Q17" t="n">
         <v>8</v>
       </c>
     </row>
@@ -1380,18 +1433,21 @@
         <v>3</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
         <v>9</v>
       </c>
-      <c r="N18" t="n">
-        <v>10</v>
-      </c>
       <c r="O18" t="n">
+        <v>10</v>
+      </c>
+      <c r="P18" t="n">
         <v>4</v>
       </c>
-      <c r="P18" t="n">
+      <c r="Q18" t="n">
         <v>8</v>
       </c>
     </row>
@@ -1432,18 +1488,21 @@
         <v>6</v>
       </c>
       <c r="L19" t="n">
+        <v>6</v>
+      </c>
+      <c r="M19" t="n">
         <v>1</v>
       </c>
-      <c r="M19" t="n">
-        <v>10</v>
-      </c>
       <c r="N19" t="n">
+        <v>10</v>
+      </c>
+      <c r="O19" t="n">
         <v>12</v>
       </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
       <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
         <v>11</v>
       </c>
     </row>
@@ -1484,18 +1543,21 @@
         <v>4</v>
       </c>
       <c r="L20" t="n">
+        <v>5</v>
+      </c>
+      <c r="M20" t="n">
         <v>1</v>
       </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
         <v>8</v>
       </c>
-      <c r="N20" t="n">
+      <c r="O20" t="n">
         <v>11</v>
       </c>
-      <c r="O20" t="n">
+      <c r="P20" t="n">
         <v>7</v>
       </c>
-      <c r="P20" t="n">
+      <c r="Q20" t="n">
         <v>10</v>
       </c>
     </row>
@@ -1536,18 +1598,21 @@
         <v>5</v>
       </c>
       <c r="L21" t="n">
+        <v>7</v>
+      </c>
+      <c r="M21" t="n">
         <v>2</v>
       </c>
-      <c r="M21" t="n">
+      <c r="N21" t="n">
         <v>9</v>
       </c>
-      <c r="N21" t="n">
-        <v>10</v>
-      </c>
       <c r="O21" t="n">
         <v>10</v>
       </c>
       <c r="P21" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q21" t="n">
         <v>10</v>
       </c>
     </row>
@@ -1600,6 +1665,9 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1640,18 +1708,21 @@
         <v>3</v>
       </c>
       <c r="L23" t="n">
+        <v>3</v>
+      </c>
+      <c r="M23" t="n">
         <v>1</v>
       </c>
-      <c r="M23" t="n">
+      <c r="N23" t="n">
         <v>11</v>
       </c>
-      <c r="N23" t="n">
-        <v>10</v>
-      </c>
       <c r="O23" t="n">
+        <v>10</v>
+      </c>
+      <c r="P23" t="n">
         <v>9</v>
       </c>
-      <c r="P23" t="n">
+      <c r="Q23" t="n">
         <v>11</v>
       </c>
     </row>
@@ -1692,18 +1763,21 @@
         <v>10</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
         <v>7</v>
-      </c>
-      <c r="N24" t="n">
-        <v>9</v>
       </c>
       <c r="O24" t="n">
         <v>9</v>
       </c>
       <c r="P24" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q24" t="n">
         <v>10</v>
       </c>
     </row>
@@ -1718,7 +1792,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P24"/>
+  <dimension ref="A1:Q24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1779,25 +1853,30 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>11dec2025</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -1828,6 +1907,7 @@
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -1882,22 +1962,23 @@
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -1949,25 +2030,30 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -2013,12 +2099,12 @@
           <t>9</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>10</t>
@@ -2026,10 +2112,15 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -2091,23 +2182,28 @@
           <t>4</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -2171,25 +2267,30 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="O7" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -2251,23 +2352,28 @@
           <t>3</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -2327,25 +2433,30 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="O9" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -2405,25 +2516,30 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -2485,23 +2601,28 @@
           <t>4</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -2557,25 +2678,30 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -2639,14 +2765,14 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr">
         <is>
           <t>10</t>
@@ -2658,6 +2784,11 @@
         </is>
       </c>
       <c r="P13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -2719,23 +2850,28 @@
           <t>5</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="O14" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="Q14" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -2797,23 +2933,28 @@
           <t>8</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -2871,27 +3012,28 @@
           <t>4</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="O16" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -2949,27 +3091,28 @@
           <t>3</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="O17" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="Q17" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -3027,23 +3170,28 @@
           <t>3</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="O18" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="Q18" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -3099,21 +3247,26 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr">
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -3177,25 +3330,30 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="Q20" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -3259,25 +3417,30 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="O21" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -3303,7 +3466,8 @@
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr">
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -3367,25 +3531,30 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="O23" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr">
+      <c r="Q23" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -3447,23 +3616,28 @@
           <t>10</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
+      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
+      <c r="P24" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr">
+      <c r="Q24" t="inlineStr">
         <is>
           <t>10</t>
         </is>

--- a/data/curva_de_sun.xlsx
+++ b/data/curva_de_sun.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q24"/>
+  <dimension ref="A1:T24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -492,25 +492,40 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>12dec2025</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>13dec2025</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>14dec2025</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -570,6 +585,15 @@
       <c r="Q2" t="n">
         <v>0</v>
       </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -611,18 +635,27 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
         <v>2</v>
       </c>
-      <c r="O3" t="n">
+      <c r="R3" t="n">
         <v>6</v>
       </c>
-      <c r="P3" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q3" t="n">
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -666,18 +699,27 @@
         <v>9</v>
       </c>
       <c r="M4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N4" t="n">
+        <v>3</v>
+      </c>
+      <c r="O4" t="n">
+        <v>7</v>
+      </c>
+      <c r="P4" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q4" t="n">
         <v>6</v>
       </c>
-      <c r="O4" t="n">
+      <c r="R4" t="n">
         <v>1</v>
       </c>
-      <c r="P4" t="n">
+      <c r="S4" t="n">
         <v>24</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="T4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -724,15 +766,24 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>10</v>
+      </c>
+      <c r="R5" t="n">
+        <v>10</v>
+      </c>
+      <c r="S5" t="n">
         <v>8</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="T5" t="n">
         <v>9</v>
       </c>
     </row>
@@ -776,18 +827,27 @@
         <v>3</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N6" t="n">
+        <v>3</v>
+      </c>
+      <c r="O6" t="n">
+        <v>3</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
         <v>6</v>
       </c>
-      <c r="O6" t="n">
+      <c r="R6" t="n">
         <v>9</v>
       </c>
-      <c r="P6" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q6" t="n">
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="n">
         <v>8</v>
       </c>
     </row>
@@ -831,18 +891,27 @@
         <v>4</v>
       </c>
       <c r="M7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N7" t="n">
+        <v>10</v>
+      </c>
+      <c r="O7" t="n">
+        <v>12</v>
+      </c>
+      <c r="P7" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q7" t="n">
         <v>6</v>
       </c>
-      <c r="O7" t="n">
-        <v>10</v>
-      </c>
-      <c r="P7" t="n">
+      <c r="R7" t="n">
+        <v>10</v>
+      </c>
+      <c r="S7" t="n">
         <v>9</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="T7" t="n">
         <v>10</v>
       </c>
     </row>
@@ -886,18 +955,27 @@
         <v>4</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N8" t="n">
+        <v>3</v>
+      </c>
+      <c r="O8" t="n">
+        <v>3</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
         <v>6</v>
       </c>
-      <c r="O8" t="n">
+      <c r="R8" t="n">
         <v>12</v>
       </c>
-      <c r="P8" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q8" t="n">
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -941,20 +1019,29 @@
         <v>6</v>
       </c>
       <c r="M9" t="n">
+        <v>2</v>
+      </c>
+      <c r="N9" t="n">
         <v>1</v>
       </c>
-      <c r="N9" t="n">
-        <v>9</v>
-      </c>
       <c r="O9" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="P9" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="Q9" t="n">
         <v>9</v>
       </c>
+      <c r="R9" t="n">
+        <v>10</v>
+      </c>
+      <c r="S9" t="n">
+        <v>9</v>
+      </c>
+      <c r="T9" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -996,18 +1083,27 @@
         <v>3</v>
       </c>
       <c r="M10" t="n">
+        <v>4</v>
+      </c>
+      <c r="N10" t="n">
+        <v>4</v>
+      </c>
+      <c r="O10" t="n">
+        <v>4</v>
+      </c>
+      <c r="P10" t="n">
         <v>2</v>
       </c>
-      <c r="N10" t="n">
-        <v>5</v>
-      </c>
-      <c r="O10" t="n">
+      <c r="Q10" t="n">
+        <v>5</v>
+      </c>
+      <c r="R10" t="n">
         <v>8</v>
       </c>
-      <c r="P10" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q10" t="n">
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="n">
         <v>10</v>
       </c>
     </row>
@@ -1051,20 +1147,29 @@
         <v>7</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="N11" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="O11" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="P11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>12</v>
       </c>
+      <c r="R11" t="n">
+        <v>11</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -1109,15 +1214,24 @@
         <v>1</v>
       </c>
       <c r="N12" t="n">
+        <v>2</v>
+      </c>
+      <c r="O12" t="n">
+        <v>2</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q12" t="n">
         <v>9</v>
       </c>
-      <c r="O12" t="n">
+      <c r="R12" t="n">
         <v>8</v>
       </c>
-      <c r="P12" t="n">
+      <c r="S12" t="n">
         <v>9</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="T12" t="n">
         <v>10</v>
       </c>
     </row>
@@ -1131,7 +1245,7 @@
         <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D13" t="n">
         <v>9</v>
@@ -1161,18 +1275,27 @@
         <v>12</v>
       </c>
       <c r="M13" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="N13" t="n">
         <v>10</v>
       </c>
       <c r="O13" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="P13" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="Q13" t="n">
+        <v>10</v>
+      </c>
+      <c r="R13" t="n">
+        <v>10</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="n">
         <v>10</v>
       </c>
     </row>
@@ -1216,18 +1339,27 @@
         <v>4</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N14" t="n">
+        <v>6</v>
+      </c>
+      <c r="O14" t="n">
+        <v>4</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
         <v>11</v>
       </c>
-      <c r="O14" t="n">
-        <v>10</v>
-      </c>
-      <c r="P14" t="n">
+      <c r="R14" t="n">
+        <v>10</v>
+      </c>
+      <c r="S14" t="n">
         <v>8</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="T14" t="n">
         <v>12</v>
       </c>
     </row>
@@ -1271,18 +1403,27 @@
         <v>6</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="N15" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="O15" t="n">
         <v>14</v>
       </c>
       <c r="P15" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
+        <v>5</v>
+      </c>
+      <c r="R15" t="n">
+        <v>14</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="n">
         <v>10</v>
       </c>
     </row>
@@ -1326,18 +1467,27 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
+        <v>5</v>
+      </c>
+      <c r="N16" t="n">
         <v>2</v>
       </c>
-      <c r="N16" t="n">
+      <c r="O16" t="n">
+        <v>2</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q16" t="n">
         <v>8</v>
       </c>
-      <c r="O16" t="n">
-        <v>10</v>
-      </c>
-      <c r="P16" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
+        <v>10</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="n">
         <v>10</v>
       </c>
     </row>
@@ -1381,18 +1531,27 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
+        <v>5</v>
+      </c>
+      <c r="N17" t="n">
         <v>2</v>
       </c>
-      <c r="N17" t="n">
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q17" t="n">
         <v>7</v>
       </c>
-      <c r="O17" t="n">
-        <v>10</v>
-      </c>
-      <c r="P17" t="n">
+      <c r="R17" t="n">
+        <v>10</v>
+      </c>
+      <c r="S17" t="n">
         <v>6</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="T17" t="n">
         <v>8</v>
       </c>
     </row>
@@ -1439,15 +1598,24 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>3</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
         <v>9</v>
       </c>
-      <c r="O18" t="n">
-        <v>10</v>
-      </c>
-      <c r="P18" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
+        <v>10</v>
+      </c>
+      <c r="S18" t="n">
+        <v>4</v>
+      </c>
+      <c r="T18" t="n">
         <v>8</v>
       </c>
     </row>
@@ -1491,18 +1659,27 @@
         <v>6</v>
       </c>
       <c r="M19" t="n">
+        <v>3</v>
+      </c>
+      <c r="N19" t="n">
+        <v>4</v>
+      </c>
+      <c r="O19" t="n">
+        <v>5</v>
+      </c>
+      <c r="P19" t="n">
         <v>1</v>
       </c>
-      <c r="N19" t="n">
-        <v>10</v>
-      </c>
-      <c r="O19" t="n">
+      <c r="Q19" t="n">
+        <v>10</v>
+      </c>
+      <c r="R19" t="n">
         <v>12</v>
       </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
         <v>11</v>
       </c>
     </row>
@@ -1546,18 +1723,27 @@
         <v>5</v>
       </c>
       <c r="M20" t="n">
+        <v>4</v>
+      </c>
+      <c r="N20" t="n">
+        <v>3</v>
+      </c>
+      <c r="O20" t="n">
+        <v>3</v>
+      </c>
+      <c r="P20" t="n">
         <v>1</v>
       </c>
-      <c r="N20" t="n">
+      <c r="Q20" t="n">
         <v>8</v>
       </c>
-      <c r="O20" t="n">
+      <c r="R20" t="n">
         <v>11</v>
       </c>
-      <c r="P20" t="n">
+      <c r="S20" t="n">
         <v>7</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="T20" t="n">
         <v>10</v>
       </c>
     </row>
@@ -1601,18 +1787,27 @@
         <v>7</v>
       </c>
       <c r="M21" t="n">
+        <v>5</v>
+      </c>
+      <c r="N21" t="n">
+        <v>3</v>
+      </c>
+      <c r="O21" t="n">
+        <v>4</v>
+      </c>
+      <c r="P21" t="n">
         <v>2</v>
       </c>
-      <c r="N21" t="n">
+      <c r="Q21" t="n">
         <v>9</v>
       </c>
-      <c r="O21" t="n">
-        <v>10</v>
-      </c>
-      <c r="P21" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
+        <v>10</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="n">
         <v>10</v>
       </c>
     </row>
@@ -1668,6 +1863,15 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1711,20 +1915,29 @@
         <v>3</v>
       </c>
       <c r="M23" t="n">
+        <v>3</v>
+      </c>
+      <c r="N23" t="n">
+        <v>3</v>
+      </c>
+      <c r="O23" t="n">
+        <v>3</v>
+      </c>
+      <c r="P23" t="n">
         <v>1</v>
-      </c>
-      <c r="N23" t="n">
-        <v>11</v>
-      </c>
-      <c r="O23" t="n">
-        <v>10</v>
-      </c>
-      <c r="P23" t="n">
-        <v>9</v>
       </c>
       <c r="Q23" t="n">
         <v>11</v>
       </c>
+      <c r="R23" t="n">
+        <v>10</v>
+      </c>
+      <c r="S23" t="n">
+        <v>9</v>
+      </c>
+      <c r="T23" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
@@ -1766,18 +1979,27 @@
         <v>7</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="N24" t="n">
+        <v>11</v>
+      </c>
+      <c r="O24" t="n">
+        <v>12</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
         <v>7</v>
       </c>
-      <c r="O24" t="n">
+      <c r="R24" t="n">
         <v>9</v>
       </c>
-      <c r="P24" t="n">
+      <c r="S24" t="n">
         <v>9</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="T24" t="n">
         <v>10</v>
       </c>
     </row>
@@ -1792,7 +2014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q24"/>
+  <dimension ref="A1:T24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1858,25 +2080,40 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>12dec2025</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>13dec2025</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>14dec2025</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -1908,6 +2145,9 @@
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -1962,23 +2202,34 @@
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr"/>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -2035,25 +2286,40 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -2105,22 +2371,29 @@
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
+          <t>13</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -2187,23 +2460,38 @@
           <t>3</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -2272,25 +2560,40 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -2357,23 +2660,38 @@
           <t>4</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr"/>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -2438,25 +2756,40 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -2521,25 +2854,40 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -2606,23 +2954,38 @@
           <t>7</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -2688,20 +3051,35 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -2720,34 +3098,34 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="I13" t="inlineStr">
         <is>
           <t>10</t>
@@ -2770,7 +3148,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2780,15 +3158,30 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -2855,23 +3248,38 @@
           <t>4</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -2938,10 +3346,14 @@
           <t>6</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>14</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -2949,12 +3361,23 @@
           <t>14</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -3015,25 +3438,40 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -3094,25 +3532,36 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -3176,22 +3625,29 @@
         </is>
       </c>
       <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr">
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -3252,21 +3708,36 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr">
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -3335,25 +3806,40 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="Q20" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
+      <c r="R20" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -3422,25 +3908,40 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="Q21" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -3467,7 +3968,10 @@
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr">
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -3536,25 +4040,40 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="Q23" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr">
+      <c r="T23" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -3621,23 +4140,38 @@
           <t>7</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
+      <c r="R24" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr">
+      <c r="S24" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr">
+      <c r="T24" t="inlineStr">
         <is>
           <t>10</t>
         </is>

--- a/data/curva_de_sun.xlsx
+++ b/data/curva_de_sun.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T24"/>
+  <dimension ref="A1:U24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,25 +507,30 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
+          <t>15dec2025</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -594,6 +599,9 @@
       <c r="T2" t="n">
         <v>0</v>
       </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -644,18 +652,21 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
         <v>2</v>
       </c>
-      <c r="R3" t="n">
+      <c r="S3" t="n">
         <v>6</v>
       </c>
-      <c r="S3" t="n">
-        <v>5</v>
-      </c>
       <c r="T3" t="n">
+        <v>5</v>
+      </c>
+      <c r="U3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -708,18 +719,21 @@
         <v>7</v>
       </c>
       <c r="P4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q4" t="n">
+        <v>3</v>
+      </c>
+      <c r="R4" t="n">
         <v>6</v>
       </c>
-      <c r="R4" t="n">
+      <c r="S4" t="n">
         <v>1</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>24</v>
       </c>
-      <c r="T4" t="n">
+      <c r="U4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -733,7 +747,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -772,18 +786,21 @@
         <v>13</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q5" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>10</v>
       </c>
       <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="n">
         <v>8</v>
       </c>
-      <c r="T5" t="n">
+      <c r="U5" t="n">
         <v>9</v>
       </c>
     </row>
@@ -836,18 +853,21 @@
         <v>3</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
         <v>6</v>
       </c>
-      <c r="R6" t="n">
+      <c r="S6" t="n">
         <v>9</v>
       </c>
-      <c r="S6" t="n">
-        <v>10</v>
-      </c>
       <c r="T6" t="n">
+        <v>10</v>
+      </c>
+      <c r="U6" t="n">
         <v>8</v>
       </c>
     </row>
@@ -900,18 +920,21 @@
         <v>12</v>
       </c>
       <c r="P7" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="Q7" t="n">
+        <v>3</v>
+      </c>
+      <c r="R7" t="n">
         <v>6</v>
       </c>
-      <c r="R7" t="n">
-        <v>10</v>
-      </c>
       <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="n">
         <v>9</v>
       </c>
-      <c r="T7" t="n">
+      <c r="U7" t="n">
         <v>10</v>
       </c>
     </row>
@@ -964,18 +987,21 @@
         <v>3</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
         <v>6</v>
       </c>
-      <c r="R8" t="n">
+      <c r="S8" t="n">
         <v>12</v>
       </c>
-      <c r="S8" t="n">
-        <v>10</v>
-      </c>
       <c r="T8" t="n">
+        <v>10</v>
+      </c>
+      <c r="U8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1028,20 +1054,23 @@
         <v>2</v>
       </c>
       <c r="P9" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q9" t="n">
         <v>1</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>9</v>
       </c>
-      <c r="R9" t="n">
-        <v>10</v>
-      </c>
       <c r="S9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T9" t="n">
         <v>9</v>
       </c>
+      <c r="U9" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -1092,18 +1121,21 @@
         <v>4</v>
       </c>
       <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
         <v>2</v>
       </c>
-      <c r="Q10" t="n">
-        <v>5</v>
-      </c>
       <c r="R10" t="n">
+        <v>5</v>
+      </c>
+      <c r="S10" t="n">
         <v>8</v>
       </c>
-      <c r="S10" t="n">
-        <v>10</v>
-      </c>
       <c r="T10" t="n">
+        <v>10</v>
+      </c>
+      <c r="U10" t="n">
         <v>10</v>
       </c>
     </row>
@@ -1156,18 +1188,21 @@
         <v>5</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
         <v>12</v>
       </c>
-      <c r="R11" t="n">
+      <c r="S11" t="n">
         <v>11</v>
       </c>
-      <c r="S11" t="n">
-        <v>10</v>
-      </c>
       <c r="T11" t="n">
+        <v>10</v>
+      </c>
+      <c r="U11" t="n">
         <v>12</v>
       </c>
     </row>
@@ -1220,18 +1255,21 @@
         <v>2</v>
       </c>
       <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
         <v>1</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>9</v>
       </c>
-      <c r="R12" t="n">
+      <c r="S12" t="n">
         <v>8</v>
       </c>
-      <c r="S12" t="n">
+      <c r="T12" t="n">
         <v>9</v>
       </c>
-      <c r="T12" t="n">
+      <c r="U12" t="n">
         <v>10</v>
       </c>
     </row>
@@ -1284,10 +1322,10 @@
         <v>12</v>
       </c>
       <c r="P13" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="Q13" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="R13" t="n">
         <v>10</v>
@@ -1296,6 +1334,9 @@
         <v>10</v>
       </c>
       <c r="T13" t="n">
+        <v>10</v>
+      </c>
+      <c r="U13" t="n">
         <v>10</v>
       </c>
     </row>
@@ -1348,18 +1389,21 @@
         <v>4</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
         <v>11</v>
       </c>
-      <c r="R14" t="n">
-        <v>10</v>
-      </c>
       <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="n">
         <v>8</v>
       </c>
-      <c r="T14" t="n">
+      <c r="U14" t="n">
         <v>12</v>
       </c>
     </row>
@@ -1412,18 +1456,21 @@
         <v>14</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q15" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
+        <v>5</v>
+      </c>
+      <c r="S15" t="n">
         <v>14</v>
       </c>
-      <c r="S15" t="n">
-        <v>10</v>
-      </c>
       <c r="T15" t="n">
+        <v>10</v>
+      </c>
+      <c r="U15" t="n">
         <v>10</v>
       </c>
     </row>
@@ -1476,18 +1523,21 @@
         <v>2</v>
       </c>
       <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
         <v>2</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>8</v>
       </c>
-      <c r="R16" t="n">
-        <v>10</v>
-      </c>
       <c r="S16" t="n">
         <v>10</v>
       </c>
       <c r="T16" t="n">
+        <v>10</v>
+      </c>
+      <c r="U16" t="n">
         <v>10</v>
       </c>
     </row>
@@ -1540,18 +1590,21 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q17" t="n">
         <v>2</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>7</v>
       </c>
-      <c r="R17" t="n">
-        <v>10</v>
-      </c>
       <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="n">
         <v>6</v>
       </c>
-      <c r="T17" t="n">
+      <c r="U17" t="n">
         <v>8</v>
       </c>
     </row>
@@ -1604,18 +1657,21 @@
         <v>3</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
         <v>9</v>
       </c>
-      <c r="R18" t="n">
-        <v>10</v>
-      </c>
       <c r="S18" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T18" t="n">
+        <v>4</v>
+      </c>
+      <c r="U18" t="n">
         <v>8</v>
       </c>
     </row>
@@ -1668,18 +1724,21 @@
         <v>5</v>
       </c>
       <c r="P19" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q19" t="n">
         <v>1</v>
       </c>
-      <c r="Q19" t="n">
-        <v>10</v>
-      </c>
       <c r="R19" t="n">
+        <v>10</v>
+      </c>
+      <c r="S19" t="n">
         <v>12</v>
       </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
       <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
         <v>11</v>
       </c>
     </row>
@@ -1732,18 +1791,21 @@
         <v>3</v>
       </c>
       <c r="P20" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q20" t="n">
         <v>1</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>8</v>
       </c>
-      <c r="R20" t="n">
-        <v>11</v>
-      </c>
       <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="n">
         <v>7</v>
       </c>
-      <c r="T20" t="n">
+      <c r="U20" t="n">
         <v>10</v>
       </c>
     </row>
@@ -1796,18 +1858,21 @@
         <v>4</v>
       </c>
       <c r="P21" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q21" t="n">
         <v>2</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>9</v>
       </c>
-      <c r="R21" t="n">
-        <v>10</v>
-      </c>
       <c r="S21" t="n">
         <v>10</v>
       </c>
       <c r="T21" t="n">
+        <v>10</v>
+      </c>
+      <c r="U21" t="n">
         <v>10</v>
       </c>
     </row>
@@ -1872,6 +1937,9 @@
         <v>0</v>
       </c>
       <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1924,18 +1992,21 @@
         <v>3</v>
       </c>
       <c r="P23" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q23" t="n">
         <v>1</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="R23" t="n">
         <v>11</v>
       </c>
-      <c r="R23" t="n">
-        <v>10</v>
-      </c>
       <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="n">
         <v>9</v>
       </c>
-      <c r="T23" t="n">
+      <c r="U23" t="n">
         <v>11</v>
       </c>
     </row>
@@ -1988,18 +2059,21 @@
         <v>12</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
         <v>7</v>
-      </c>
-      <c r="R24" t="n">
-        <v>9</v>
       </c>
       <c r="S24" t="n">
         <v>9</v>
       </c>
       <c r="T24" t="n">
+        <v>9</v>
+      </c>
+      <c r="U24" t="n">
         <v>10</v>
       </c>
     </row>
@@ -2014,7 +2088,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T24"/>
+  <dimension ref="A1:U24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2095,25 +2169,30 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
+          <t>15dec2025</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -2148,6 +2227,7 @@
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -2213,23 +2293,28 @@
         </is>
       </c>
       <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr">
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr"/>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -2301,25 +2386,30 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -2334,7 +2424,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -2377,12 +2467,12 @@
           <t>13</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
           <t>10</t>
@@ -2390,10 +2480,15 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -2475,23 +2570,28 @@
           <t>3</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr">
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="T6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -2575,25 +2675,30 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="S7" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -2675,23 +2780,28 @@
           <t>3</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr">
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr"/>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -2771,25 +2881,30 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="S9" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -2867,27 +2982,28 @@
           <t>4</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="R10" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="T10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -2969,23 +3085,28 @@
           <t>5</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr">
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="T11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -3059,27 +3180,28 @@
           <t>2</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -3163,12 +3285,12 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>17</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -3182,6 +3304,11 @@
         </is>
       </c>
       <c r="T13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -3263,23 +3390,28 @@
           <t>4</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr">
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="S14" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -3361,23 +3493,28 @@
           <t>14</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="T15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -3451,27 +3588,28 @@
           <t>2</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr">
+      <c r="R16" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="S16" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -3543,25 +3681,30 @@
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr">
+      <c r="R17" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="S17" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -3631,23 +3774,28 @@
           <t>3</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr">
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -3723,21 +3871,26 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="R19" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr">
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -3821,25 +3974,30 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr">
+      <c r="R20" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="S20" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -3923,25 +4081,30 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr">
+      <c r="R21" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="S21" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -3971,7 +4134,8 @@
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr"/>
-      <c r="T22" t="inlineStr">
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -4055,25 +4219,30 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr">
+      <c r="R23" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="S23" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr">
+      <c r="U23" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -4155,23 +4324,28 @@
           <t>12</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr">
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr">
+      <c r="S24" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr">
+      <c r="T24" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr">
+      <c r="U24" t="inlineStr">
         <is>
           <t>10</t>
         </is>
